--- a/demo.ig/StructureDefinition-demo-patient.xlsx
+++ b/demo.ig/StructureDefinition-demo-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-24T16:10:15+01:00</t>
+    <t>2026-01-03T14:02:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
